--- a/news_daily/2026-08-09.xlsx
+++ b/news_daily/2026-08-09.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -1473,13 +1473,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1536,7 +1540,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>1443ee69f56e4ef0bd40975d9097ea5a</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>05ea2f18bd4f2851b43711a7</t>
@@ -1557,7 +1565,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -1603,8 +1615,16 @@
       <c r="BH5" s="3" t="inlineStr"/>
       <c r="BI5" s="3" t="inlineStr"/>
       <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr"/>
-      <c r="BL5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1987,186 +2007,202 @@
       <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>EchoStar</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-08-09T22:07:32+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Deal wins playoff over Bair for Echo Hills Club Championship title</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.638</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeDRad0wtclZ2NmJWRnpFLUZCS240ZEFUM2dIYmMwQWwtcV92a25vcFVaMmlCRGVVREhOZkNZQnRfa1J3eWlfZWRSWGNEcnJsT1dOd3NvVHRkbmlBaTRaV0Y1N0R4NFNoakRpc1BUSld5SlBBR0hHU0FvUW9YbHp2WUZzcklfNWZSN1lQbEtCbGNfV05IbW5MWnFFR2Y?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Miami Valley Today</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>迪爾在延長賽中擊敗貝爾，奪得迴聲山俱樂部錦標賽冠軍</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>layoff</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>699b698a02c843959484a6b3243fe722</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>1f19875bdcd0ab2b6dd34fe2</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>c2bdafc09c6b8f06461d7001</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" s="2" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" s="2" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>0.638</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="AP8" s="2" t="inlineStr"/>
+      <c r="AQ8" s="2" t="inlineStr"/>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="inlineStr"/>
+      <c r="AT8" s="2" t="inlineStr"/>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" s="2" t="inlineStr"/>
+      <c r="AX8" s="2" t="inlineStr"/>
+      <c r="AY8" s="2" t="inlineStr"/>
+      <c r="AZ8" s="2" t="inlineStr"/>
+      <c r="BA8" s="2" t="inlineStr"/>
+      <c r="BB8" s="2" t="inlineStr">
+        <is>
+          <t>ECHO</t>
+        </is>
+      </c>
+      <c r="BC8" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeDRad0wtclZ2NmJWRnpFLUZCS240ZEFUM2dIYmMwQWwtcV92a25vcFVaMmlCRGVVREhOZkNZQnRfa1J3eWlfZWRSWGNEcnJsT1dOd3NvVHRkbmlBaTRaV0Y1N0R4NFNoakRpc1BUSld5SlBBR0hHU0FvUW9YbHp2WUZzcklfNWZSN1lQbEtCbGNfV05IbW5MWnFFR2Y?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>Miami Valley Today</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t>迪爾在延長賽中擊敗貝爾，奪得迴聲山俱樂部錦標賽冠軍</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>1f19875bdcd0ab2b6dd34fe2</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>c2bdafc09c6b8f06461d7001</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr"/>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
+      <c r="BD8" s="2" t="inlineStr">
         <is>
           <t>ECHO</t>
         </is>
       </c>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD8" s="3" t="inlineStr">
-        <is>
-          <t>ECHO</t>
-        </is>
-      </c>
-      <c r="BE8" s="3" t="inlineStr">
+      <c r="BE8" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr"/>
-      <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr"/>
-      <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr"/>
-      <c r="BL8" s="3" t="inlineStr"/>
+      <c r="BG8" s="2" t="inlineStr"/>
+      <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2545,368 +2581,416 @@
       <c r="BL10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>FDX</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>FedEx Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>2026-08-09T20:40:42+08:00</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Alex Fitzpatrick is ready to go deep in his first FedEx Cup playoffs run</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.302</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQSU9ybDZaZmJVZlhrbW1JSkJGcGlnc2xGTTFFZjAtZHNGbW4xSVhNSXRxMVlyVW9PbFpuTHgta1o0QXRQMnk5dUdLcGoyYjIxaXY0a1lPZmNaOWp0UERqNEZiWHhOUDlXSF9XblFDTzlKRGZ2VjEycFJheEpTMEtDRC1aa1FFd21aTXl2TkFn?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>GOLF.com</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>亞歷克斯·菲茨帕特里克（Alex Fitzpatrick）已準備好在他的第一次聯邦快遞杯季後賽中走得更遠</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>d07678ab86ce48619e0d64535f566f18</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>7bfea9cf408b7de8f418e2ca</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>ed77bc1b0a1dcb3c2e4c6b4b</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AK11" s="2" t="inlineStr"/>
+      <c r="AL11" s="2" t="inlineStr"/>
+      <c r="AM11" s="2" t="inlineStr"/>
+      <c r="AN11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>0.302</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQSU9ybDZaZmJVZlhrbW1JSkJGcGlnc2xGTTFFZjAtZHNGbW4xSVhNSXRxMVlyVW9PbFpuTHgta1o0QXRQMnk5dUdLcGoyYjIxaXY0a1lPZmNaOWp0UERqNEZiWHhOUDlXSF9XblFDTzlKRGZ2VjEycFJheEpTMEtDRC1aa1FFd21aTXl2TkFn?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>GOLF.com</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t>亞歷克斯·菲茨帕特里克（Alex Fitzpatrick）已準備好在他的第一次聯邦快遞杯季後賽中走得更遠</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>7bfea9cf408b7de8f418e2ca</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>ed77bc1b0a1dcb3c2e4c6b4b</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr">
+      <c r="AP11" s="2" t="inlineStr"/>
+      <c r="AQ11" s="2" t="inlineStr"/>
+      <c r="AR11" s="2" t="inlineStr"/>
+      <c r="AS11" s="2" t="inlineStr"/>
+      <c r="AT11" s="2" t="inlineStr"/>
+      <c r="AU11" s="2" t="inlineStr"/>
+      <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
+      <c r="AX11" s="2" t="inlineStr"/>
+      <c r="AY11" s="2" t="inlineStr"/>
+      <c r="AZ11" s="2" t="inlineStr"/>
+      <c r="BA11" s="2" t="inlineStr"/>
+      <c r="BB11" s="2" t="inlineStr">
         <is>
           <t>FDX</t>
         </is>
       </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="BC11" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
+      <c r="BD11" s="2" t="inlineStr"/>
+      <c r="BE11" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF11" s="3" t="inlineStr">
+      <c r="BF11" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG11" s="3" t="inlineStr">
+      <c r="BG11" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr"/>
-      <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr"/>
-      <c r="BL11" s="3" t="inlineStr"/>
+      <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Meta Platforms, Inc.</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2026-08-09T19:09:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>I went from wedding DJ to Meta engineer, then was laid off after 13 years. My last years there brought constant change.</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>'-0.302</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOeGdTcDRTQWVRQ1NqcWZ2ZkpVemtWOE0yaGlpOVNjVXk5d3ZxSjh6elJ6WWNyVTROWlBaUkVfTlZRX1RJeUhTdW50NGtwaEZ1VncxSi13cVRBTm80NlVudkRoR2RwbUZkNXhaLWhtU29vT3I2bmNOV2ItQ1BvVHNtcDVUYmZtZHpzd1h6eFNtcXl2a3Rkbm9VcGUyR1ZsR04tWUFpeQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>businessinsider.com</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>我從婚禮 DJ 到 Meta 工程師，13 年後被解僱。我在那裡的最後幾年帶來了不斷的變化。</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>laid off</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>10900000</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>9b8a25d9eeaa4e9ba6baa11261cf8795</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>431c52efe5ad951117d3c27a</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>8e03bc4197a55663030cac41</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>'-0.302</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOeGdTcDRTQWVRQ1NqcWZ2ZkpVemtWOE0yaGlpOVNjVXk5d3ZxSjh6elJ6WWNyVTROWlBaUkVfTlZRX1RJeUhTdW50NGtwaEZ1VncxSi13cVRBTm80NlVudkRoR2RwbUZkNXhaLWhtU29vT3I2bmNOV2ItQ1BvVHNtcDVUYmZtZHpzd1h6eFNtcXl2a3Rkbm9VcGUyR1ZsR04tWUFpeQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>businessinsider.com</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t>我從婚禮 DJ 到 Meta 工程師，13 年後被解僱。我在那裡的最後幾年帶來了不斷的變化。</t>
-        </is>
-      </c>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>laid off</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr">
-        <is>
-          <t>10900000</t>
-        </is>
-      </c>
-      <c r="AB12" s="3" t="inlineStr"/>
-      <c r="AC12" s="3" t="inlineStr">
-        <is>
-          <t>431c52efe5ad951117d3c27a</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>8e03bc4197a55663030cac41</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AP12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="inlineStr"/>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="BC12" s="3" t="inlineStr">
+      <c r="BC12" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
+      <c r="BD12" s="2" t="inlineStr"/>
+      <c r="BE12" s="2" t="inlineStr">
         <is>
           <t>https://investor.atmeta.com/stock-info/default.aspx</t>
         </is>
       </c>
-      <c r="BF12" s="3" t="inlineStr">
+      <c r="BF12" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BG12" s="2" t="inlineStr">
         <is>
           <t>上市公司</t>
         </is>
       </c>
-      <c r="BH12" s="3" t="inlineStr"/>
-      <c r="BI12" s="3" t="inlineStr"/>
-      <c r="BJ12" s="3" t="inlineStr"/>
-      <c r="BK12" s="3" t="inlineStr"/>
-      <c r="BL12" s="3" t="inlineStr"/>
+      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3293,352 +3377,400 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Electronic Arts</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-08-09T18:54:48+08:00</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Purchase of Electronic Arts by Saudi group generates warning of mass layoffs</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>'-0.955</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQVmZ3QzhqTThuZWtzLV9NV0ZyLWtManYxS1liZF9ncUZsM0VSSHprY0Qza1ByQkFsNkI2UVdqM2hoaUZjblN5NExURENFOEZuTUw2MUg2OTZXd1VEVW9aS1lVbUNjajQwNkJfWHBQNHdBM21PR2hKdkNMNlJ6SDdvaTg2V3lVWVhJXzJtUTVYdm1XbXVmZFBYUk9oTzB2WFJxWHlRRG9UaHpyRGp0dFR0a0RqRFdOM3FVNWfSAb8BQVVfeXFMTmc4czN3QTE0TlJ4VXJXODYydmNHOUd3VFgxT0NsTWo1bG1MVk9Xd0VhYUlJX2hId0hzeXdXYXdMOFVpM2p0VW1JcE9OMnRvYllId2l5Umd2UzB0RUJWWUlEUmd4UkhWZEZmRUt1d2FuOUd5WGN1QnQ0bC13ZFJvOUt5c0dfSDRUUGdvaGpoNGlWRU5xbHBsQ1gxaHA5M3k4REtfLWtRWGd6dHJGd05mYzJsSHRLX1dFRlRwQm9sX1E?oc=5</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Mix Vale</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>沙烏地阿拉伯集團收購美國藝電公司引發大規模裁員警告</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>2f44654d945a4c80bb5619cb50014491</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>ed6d1fe8449d2d1dfa7746f1</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>9802e53e707a47fde34f073b</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr"/>
+      <c r="AL15" s="2" t="inlineStr"/>
+      <c r="AM15" s="2" t="inlineStr"/>
+      <c r="AN15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>'-0.955</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQVmZ3QzhqTThuZWtzLV9NV0ZyLWtManYxS1liZF9ncUZsM0VSSHprY0Qza1ByQkFsNkI2UVdqM2hoaUZjblN5NExURENFOEZuTUw2MUg2OTZXd1VEVW9aS1lVbUNjajQwNkJfWHBQNHdBM21PR2hKdkNMNlJ6SDdvaTg2V3lVWVhJXzJtUTVYdm1XbXVmZFBYUk9oTzB2WFJxWHlRRG9UaHpyRGp0dFR0a0RqRFdOM3FVNWfSAb8BQVVfeXFMTmc4czN3QTE0TlJ4VXJXODYydmNHOUd3VFgxT0NsTWo1bG1MVk9Xd0VhYUlJX2hId0hzeXdXYXdMOFVpM2p0VW1JcE9OMnRvYllId2l5Umd2UzB0RUJWWUlEUmd4UkhWZEZmRUt1d2FuOUd5WGN1QnQ0bC13ZFJvOUt5c0dfSDRUUGdvaGpoNGlWRU5xbHBsQ1gxaHA5M3k4REtfLWtRWGd6dHJGd05mYzJsSHRLX1dFRlRwQm9sX1E?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t>Mix Vale</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t>沙烏地阿拉伯集團收購美國藝電公司引發大規模裁員警告</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA15" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="3" t="inlineStr">
-        <is>
-          <t>ed6d1fe8449d2d1dfa7746f1</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>9802e53e707a47fde34f073b</t>
-        </is>
-      </c>
-      <c r="AE15" s="3" t="inlineStr"/>
-      <c r="AF15" s="3" t="inlineStr"/>
-      <c r="AG15" s="3" t="inlineStr"/>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-      <c r="AK15" s="3" t="inlineStr"/>
-      <c r="AL15" s="3" t="inlineStr"/>
-      <c r="AM15" s="3" t="inlineStr"/>
-      <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
-      <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="inlineStr"/>
-      <c r="AX15" s="3" t="inlineStr"/>
-      <c r="AY15" s="3" t="inlineStr"/>
-      <c r="AZ15" s="3" t="inlineStr"/>
-      <c r="BA15" s="3" t="inlineStr"/>
-      <c r="BB15" s="3" t="inlineStr">
+      <c r="AP15" s="2" t="inlineStr"/>
+      <c r="AQ15" s="2" t="inlineStr"/>
+      <c r="AR15" s="2" t="inlineStr"/>
+      <c r="AS15" s="2" t="inlineStr"/>
+      <c r="AT15" s="2" t="inlineStr"/>
+      <c r="AU15" s="2" t="inlineStr"/>
+      <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" s="2" t="inlineStr"/>
+      <c r="AX15" s="2" t="inlineStr"/>
+      <c r="AY15" s="2" t="inlineStr"/>
+      <c r="AZ15" s="2" t="inlineStr"/>
+      <c r="BA15" s="2" t="inlineStr"/>
+      <c r="BB15" s="2" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="BC15" s="3" t="inlineStr">
+      <c r="BC15" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD15" s="3" t="inlineStr"/>
-      <c r="BE15" s="3" t="inlineStr">
+      <c r="BD15" s="2" t="inlineStr"/>
+      <c r="BE15" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF15" s="3" t="inlineStr"/>
-      <c r="BG15" s="3" t="inlineStr">
+      <c r="BF15" s="2" t="inlineStr"/>
+      <c r="BG15" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH15" s="3" t="inlineStr"/>
-      <c r="BI15" s="3" t="inlineStr"/>
-      <c r="BJ15" s="3" t="inlineStr"/>
-      <c r="BK15" s="3" t="inlineStr"/>
-      <c r="BL15" s="3" t="inlineStr"/>
+      <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Electronic Arts</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>2026-08-09T18:42:04+08:00</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Purchase of Electronic Arts by Arabs generates huge debt and risk of layoffs</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>'-0.957</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPWG5BWmZXUmM1eUFLNlgzbnFSby0tNndlYmRFN0c1ZW53Q3BkZ3lwbElQdGpILU1rV2hrY01qSDN5TlBhWWVWX1R4RnVyWUs0Y2NzOU9OcktleVBaYlc4Z3M3T3dqOEZSU292QmZ4ajVQM1lucG14bmtGU3FRakJ1ZFk1YnlDNXNZNUFGd2VhZUZkQTZpb1R1cUNGakFHR2llYmExQ0pBQmxwejFLY19aS2pzUllKWUc5M0ZNVGVPMNIBvwFBVV95cUxPWG5BWmZXUmM1eUFLNlgzbnFSby0tNndlYmRFN0c1ZW53Q3BkZ3lwbElQdGpILU1rV2hrY01qSDN5TlBhWWVWX1R4RnVyWUs0Y2NzOU9OcktleVBaYlc4Z3M3T3dqOEZSU292QmZ4ajVQM1lucG14bmtGU3FRakJ1ZFk1YnlDNXNZNUFGd2VhZUZkQTZpb1R1cUNGakFHR2llYmExQ0pBQmxwejFLY19aS2pzUllKWUc5M0ZNVGVPMA?oc=5</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mix Vale</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>阿拉伯人購買電子藝界產生巨額債務和裁員風險</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>978385b678854e88b6e24aa1863c0b60</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>d0244f171d6d53b850bba8b6</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>e34c38cf5b7e2c7d5bad963e</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+      <c r="AK16" s="2" t="inlineStr"/>
+      <c r="AL16" s="2" t="inlineStr"/>
+      <c r="AM16" s="2" t="inlineStr"/>
+      <c r="AN16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>'-0.957</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
-      <c r="T16" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPWG5BWmZXUmM1eUFLNlgzbnFSby0tNndlYmRFN0c1ZW53Q3BkZ3lwbElQdGpILU1rV2hrY01qSDN5TlBhWWVWX1R4RnVyWUs0Y2NzOU9OcktleVBaYlc4Z3M3T3dqOEZSU292QmZ4ajVQM1lucG14bmtGU3FRakJ1ZFk1YnlDNXNZNUFGd2VhZUZkQTZpb1R1cUNGakFHR2llYmExQ0pBQmxwejFLY19aS2pzUllKWUc5M0ZNVGVPMNIBvwFBVV95cUxPWG5BWmZXUmM1eUFLNlgzbnFSby0tNndlYmRFN0c1ZW53Q3BkZ3lwbElQdGpILU1rV2hrY01qSDN5TlBhWWVWX1R4RnVyWUs0Y2NzOU9OcktleVBaYlc4Z3M3T3dqOEZSU292QmZ4ajVQM1lucG14bmtGU3FRakJ1ZFk1YnlDNXNZNUFGd2VhZUZkQTZpb1R1cUNGakFHR2llYmExQ0pBQmxwejFLY19aS2pzUllKWUc5M0ZNVGVPMA?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t>Mix Vale</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t>阿拉伯人購買電子藝界產生巨額債務和裁員風險</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA16" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="3" t="inlineStr"/>
-      <c r="AC16" s="3" t="inlineStr">
-        <is>
-          <t>d0244f171d6d53b850bba8b6</t>
-        </is>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>e34c38cf5b7e2c7d5bad963e</t>
-        </is>
-      </c>
-      <c r="AE16" s="3" t="inlineStr"/>
-      <c r="AF16" s="3" t="inlineStr"/>
-      <c r="AG16" s="3" t="inlineStr"/>
-      <c r="AH16" s="3" t="inlineStr"/>
-      <c r="AI16" s="3" t="inlineStr"/>
-      <c r="AJ16" s="3" t="inlineStr"/>
-      <c r="AK16" s="3" t="inlineStr"/>
-      <c r="AL16" s="3" t="inlineStr"/>
-      <c r="AM16" s="3" t="inlineStr"/>
-      <c r="AN16" s="3" t="inlineStr"/>
-      <c r="AO16" s="3" t="inlineStr"/>
-      <c r="AP16" s="3" t="inlineStr"/>
-      <c r="AQ16" s="3" t="inlineStr"/>
-      <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="inlineStr"/>
-      <c r="AV16" s="3" t="inlineStr"/>
-      <c r="AW16" s="3" t="inlineStr"/>
-      <c r="AX16" s="3" t="inlineStr"/>
-      <c r="AY16" s="3" t="inlineStr"/>
-      <c r="AZ16" s="3" t="inlineStr"/>
-      <c r="BA16" s="3" t="inlineStr"/>
-      <c r="BB16" s="3" t="inlineStr">
+      <c r="AP16" s="2" t="inlineStr"/>
+      <c r="AQ16" s="2" t="inlineStr"/>
+      <c r="AR16" s="2" t="inlineStr"/>
+      <c r="AS16" s="2" t="inlineStr"/>
+      <c r="AT16" s="2" t="inlineStr"/>
+      <c r="AU16" s="2" t="inlineStr"/>
+      <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" s="2" t="inlineStr"/>
+      <c r="AX16" s="2" t="inlineStr"/>
+      <c r="AY16" s="2" t="inlineStr"/>
+      <c r="AZ16" s="2" t="inlineStr"/>
+      <c r="BA16" s="2" t="inlineStr"/>
+      <c r="BB16" s="2" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="BC16" s="3" t="inlineStr">
+      <c r="BC16" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD16" s="3" t="inlineStr"/>
-      <c r="BE16" s="3" t="inlineStr">
+      <c r="BD16" s="2" t="inlineStr"/>
+      <c r="BE16" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF16" s="3" t="inlineStr"/>
-      <c r="BG16" s="3" t="inlineStr">
+      <c r="BF16" s="2" t="inlineStr"/>
+      <c r="BG16" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH16" s="3" t="inlineStr"/>
-      <c r="BI16" s="3" t="inlineStr"/>
-      <c r="BJ16" s="3" t="inlineStr"/>
-      <c r="BK16" s="3" t="inlineStr"/>
-      <c r="BL16" s="3" t="inlineStr"/>
+      <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3689,13 +3821,17 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3752,7 +3888,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="3" t="inlineStr"/>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>02a79b9a3a3a4b6d8d167bebc1b9476d</t>
+        </is>
+      </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
           <t>29a92f5e77588e2b98a8c624</t>
@@ -3773,7 +3913,11 @@
       <c r="AL17" s="3" t="inlineStr"/>
       <c r="AM17" s="3" t="inlineStr"/>
       <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr"/>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="3" t="inlineStr"/>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr"/>
@@ -3811,8 +3955,16 @@
       <c r="BH17" s="3" t="inlineStr"/>
       <c r="BI17" s="3" t="inlineStr"/>
       <c r="BJ17" s="3" t="inlineStr"/>
-      <c r="BK17" s="3" t="inlineStr"/>
-      <c r="BL17" s="3" t="inlineStr"/>
+      <c r="BK17" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4555,186 +4707,210 @@
       <c r="BL21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>2026-08-09T17:00:00+08:00</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Microsoft releases Windows XP patch for WannaCrypt ransomware</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>資安攻擊</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>'-0.128</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9NZ2RVR0VfTUUyS2lzbmVEaWpmb3BsUWRyWjBkRko3WnJvVllhZlR1NVdwUG9VVmo2bnJZMDdVQ3RMTUNsckp0YWg1bnFqZ2dRMFNkbzd6akU2SDYtQkJyVE9ZRThBdjhO?oc=5</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Mashable</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>微軟發布針對 WannaCrypt 勒索軟體的 Windows XP 補丁</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>ransomware</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>95500380</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>db0b78ade2ca4fdd9369c60affe10aa3</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>f1c7e7eb799e067053d54d0c</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>92d1743eeade3cb6fad4a889</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+      <c r="AK22" s="2" t="inlineStr"/>
+      <c r="AL22" s="2" t="inlineStr"/>
+      <c r="AM22" s="2" t="inlineStr"/>
+      <c r="AN22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>'-0.128</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr"/>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9NZ2RVR0VfTUUyS2lzbmVEaWpmb3BsUWRyWjBkRko3WnJvVllhZlR1NVdwUG9VVmo2bnJZMDdVQ3RMTUNsckp0YWg1bnFqZ2dRMFNkbzd6akU2SDYtQkJyVE9ZRThBdjhO?oc=5</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t>Mashable</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t>微軟發布針對 WannaCrypt 勒索軟體的 Windows XP 補丁</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>CYBER_ATTACK</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t>ransomware</t>
-        </is>
-      </c>
-      <c r="AA22" s="3" t="inlineStr">
-        <is>
-          <t>95500380</t>
-        </is>
-      </c>
-      <c r="AB22" s="3" t="inlineStr"/>
-      <c r="AC22" s="3" t="inlineStr">
-        <is>
-          <t>f1c7e7eb799e067053d54d0c</t>
-        </is>
-      </c>
-      <c r="AD22" s="3" t="inlineStr">
-        <is>
-          <t>92d1743eeade3cb6fad4a889</t>
-        </is>
-      </c>
-      <c r="AE22" s="3" t="inlineStr"/>
-      <c r="AF22" s="3" t="inlineStr"/>
-      <c r="AG22" s="3" t="inlineStr"/>
-      <c r="AH22" s="3" t="inlineStr"/>
-      <c r="AI22" s="3" t="inlineStr"/>
-      <c r="AJ22" s="3" t="inlineStr"/>
-      <c r="AK22" s="3" t="inlineStr"/>
-      <c r="AL22" s="3" t="inlineStr"/>
-      <c r="AM22" s="3" t="inlineStr"/>
-      <c r="AN22" s="3" t="inlineStr"/>
-      <c r="AO22" s="3" t="inlineStr"/>
-      <c r="AP22" s="3" t="inlineStr"/>
-      <c r="AQ22" s="3" t="inlineStr"/>
-      <c r="AR22" s="3" t="inlineStr"/>
-      <c r="AS22" s="3" t="inlineStr"/>
-      <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="inlineStr"/>
-      <c r="AV22" s="3" t="inlineStr"/>
-      <c r="AW22" s="3" t="inlineStr">
+      <c r="AP22" s="2" t="inlineStr"/>
+      <c r="AQ22" s="2" t="inlineStr"/>
+      <c r="AR22" s="2" t="inlineStr"/>
+      <c r="AS22" s="2" t="inlineStr"/>
+      <c r="AT22" s="2" t="inlineStr"/>
+      <c r="AU22" s="2" t="inlineStr"/>
+      <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX22" s="3" t="inlineStr"/>
-      <c r="AY22" s="3" t="inlineStr"/>
-      <c r="AZ22" s="3" t="inlineStr"/>
-      <c r="BA22" s="3" t="inlineStr"/>
-      <c r="BB22" s="3" t="inlineStr">
+      <c r="AX22" s="2" t="inlineStr"/>
+      <c r="AY22" s="2" t="inlineStr"/>
+      <c r="AZ22" s="2" t="inlineStr"/>
+      <c r="BA22" s="2" t="inlineStr"/>
+      <c r="BB22" s="2" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="BC22" s="3" t="inlineStr">
+      <c r="BC22" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD22" s="3" t="inlineStr"/>
-      <c r="BE22" s="3" t="inlineStr">
+      <c r="BD22" s="2" t="inlineStr"/>
+      <c r="BE22" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF22" s="3" t="inlineStr">
+      <c r="BF22" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG22" s="3" t="inlineStr">
+      <c r="BG22" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH22" s="3" t="inlineStr"/>
-      <c r="BI22" s="3" t="inlineStr"/>
-      <c r="BJ22" s="3" t="inlineStr"/>
-      <c r="BK22" s="3" t="inlineStr"/>
-      <c r="BL22" s="3" t="inlineStr"/>
+      <c r="BH22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4766,32 +4942,32 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4835,7 +5011,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -4848,7 +5024,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>2314a3f329b64138865c312f65b30659</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>cd5d4e0cf1ff0e21b41ac4fc</t>
@@ -4871,7 +5051,7 @@
       <c r="AN23" s="2" t="inlineStr"/>
       <c r="AO23" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP23" s="2" t="inlineStr"/>
@@ -4913,192 +5093,228 @@
       </c>
       <c r="BG23" s="2" t="inlineStr"/>
       <c r="BH23" s="2" t="inlineStr"/>
-      <c r="BI23" s="2" t="inlineStr"/>
+      <c r="BI23" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ23" s="2" t="inlineStr"/>
-      <c r="BK23" s="2" t="inlineStr"/>
-      <c r="BL23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Meta Platforms, Inc.</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>2026-08-09T16:05:00+08:00</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Cathie Wood's Ark Piled Into Nvidia and Taiwan Semiconductor After Meta's Earnings Miss. Here's What It Signals for Artificial Intelligence (AI) Stocks.</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPb0d5bGJQOS1EY1FQUjMzcDRnZEVod1NwS2dJRUhraElXbTY3aXQ5Zk5uOXRJWDd2NUxIaEprejl5a2VjWTF0VS1BNlZQWnRUTnF6OG9mQl95YjgwMUtfNmRiNlpiWXRmOHctVXZ6NEI3WERiNkdwWVFJZjRRYjRVdk5aeWlTeElvR3dVeWtVX2l0ckRmVG9kNg?oc=5</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>The Motley Fool</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>Meta 的獲利未達標後，Cathie Wood 的方舟紛紛買進英偉達和台積電。以下是人工智慧 (AI) 股票的訊號。</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>earnings miss</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>10900000</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>b96c25a8f03e42a5a82ccc84c208371b</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>40397b1a8e3afd65041296c3</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>705eabf69f239b628c12d34f</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+      <c r="AK24" s="2" t="inlineStr"/>
+      <c r="AL24" s="2" t="inlineStr"/>
+      <c r="AM24" s="2" t="inlineStr"/>
+      <c r="AN24" s="2" t="inlineStr"/>
+      <c r="AO24" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="3" t="inlineStr"/>
-      <c r="R24" s="3" t="inlineStr"/>
-      <c r="S24" s="3" t="inlineStr"/>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPb0d5bGJQOS1EY1FQUjMzcDRnZEVod1NwS2dJRUhraElXbTY3aXQ5Zk5uOXRJWDd2NUxIaEprejl5a2VjWTF0VS1BNlZQWnRUTnF6OG9mQl95YjgwMUtfNmRiNlpiWXRmOHctVXZ6NEI3WERiNkdwWVFJZjRRYjRVdk5aeWlTeElvR3dVeWtVX2l0ckRmVG9kNg?oc=5</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t>The Motley Fool</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t>Meta 的獲利未達標後，Cathie Wood 的方舟紛紛買進英偉達和台積電。以下是人工智慧 (AI) 股票的訊號。</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>earnings miss</t>
-        </is>
-      </c>
-      <c r="AA24" s="3" t="inlineStr">
-        <is>
-          <t>10900000</t>
-        </is>
-      </c>
-      <c r="AB24" s="3" t="inlineStr"/>
-      <c r="AC24" s="3" t="inlineStr">
-        <is>
-          <t>40397b1a8e3afd65041296c3</t>
-        </is>
-      </c>
-      <c r="AD24" s="3" t="inlineStr">
-        <is>
-          <t>705eabf69f239b628c12d34f</t>
-        </is>
-      </c>
-      <c r="AE24" s="3" t="inlineStr"/>
-      <c r="AF24" s="3" t="inlineStr"/>
-      <c r="AG24" s="3" t="inlineStr"/>
-      <c r="AH24" s="3" t="inlineStr"/>
-      <c r="AI24" s="3" t="inlineStr"/>
-      <c r="AJ24" s="3" t="inlineStr"/>
-      <c r="AK24" s="3" t="inlineStr"/>
-      <c r="AL24" s="3" t="inlineStr"/>
-      <c r="AM24" s="3" t="inlineStr"/>
-      <c r="AN24" s="3" t="inlineStr"/>
-      <c r="AO24" s="3" t="inlineStr"/>
-      <c r="AP24" s="3" t="inlineStr"/>
-      <c r="AQ24" s="3" t="inlineStr"/>
-      <c r="AR24" s="3" t="inlineStr"/>
-      <c r="AS24" s="3" t="inlineStr"/>
-      <c r="AT24" s="3" t="inlineStr"/>
-      <c r="AU24" s="3" t="inlineStr"/>
-      <c r="AV24" s="3" t="inlineStr"/>
-      <c r="AW24" s="3" t="inlineStr">
+      <c r="AP24" s="2" t="inlineStr"/>
+      <c r="AQ24" s="2" t="inlineStr"/>
+      <c r="AR24" s="2" t="inlineStr"/>
+      <c r="AS24" s="2" t="inlineStr"/>
+      <c r="AT24" s="2" t="inlineStr"/>
+      <c r="AU24" s="2" t="inlineStr"/>
+      <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX24" s="3" t="inlineStr"/>
-      <c r="AY24" s="3" t="inlineStr"/>
-      <c r="AZ24" s="3" t="inlineStr"/>
-      <c r="BA24" s="3" t="inlineStr"/>
-      <c r="BB24" s="3" t="inlineStr">
+      <c r="AX24" s="2" t="inlineStr"/>
+      <c r="AY24" s="2" t="inlineStr"/>
+      <c r="AZ24" s="2" t="inlineStr"/>
+      <c r="BA24" s="2" t="inlineStr"/>
+      <c r="BB24" s="2" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="BC24" s="3" t="inlineStr">
+      <c r="BC24" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD24" s="3" t="inlineStr"/>
-      <c r="BE24" s="3" t="inlineStr">
+      <c r="BD24" s="2" t="inlineStr"/>
+      <c r="BE24" s="2" t="inlineStr">
         <is>
           <t>https://investor.atmeta.com/stock-info/default.aspx</t>
         </is>
       </c>
-      <c r="BF24" s="3" t="inlineStr">
+      <c r="BF24" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="BG24" s="3" t="inlineStr">
+      <c r="BG24" s="2" t="inlineStr">
         <is>
           <t>上市公司</t>
         </is>
       </c>
-      <c r="BH24" s="3" t="inlineStr"/>
-      <c r="BI24" s="3" t="inlineStr"/>
-      <c r="BJ24" s="3" t="inlineStr"/>
-      <c r="BK24" s="3" t="inlineStr"/>
-      <c r="BL24" s="3" t="inlineStr"/>
+      <c r="BH24" s="2" t="inlineStr"/>
+      <c r="BI24" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ24" s="2" t="inlineStr"/>
+      <c r="BK24" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5283,186 +5499,210 @@
       <c r="BL25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>2026-08-09T15:25:00+08:00</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Cathie Wood's Ark Piled Into Nvidia and Taiwan Semiconductor After Meta's Earnings Miss. Here's What It Signals for Artificial Intelligence (AI) Stocks.</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxObjRCOVFHWFRBVlhfMVVrbVl1cTB5MG1NZkZpV1V6ZlJoLUF5RnBuN0JBTFJDeVg3MC1vdU5JbGZ1UndMT3VvU2ozXzhKVGtvMFVodEFQSlZzOXFfYmFPV2o2bG8xMjI4Q0h2N1ZkS1Z4RVJ2a1dlQ3NNTUNhZHVlSVkxcnRZNWRNc1kxdVVadkRQLVZodUtNcDJn?oc=5</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>Meta 的獲利未達標後，Cathie Wood 的方舟紛紛買進英偉達和台積電。以下是人工智慧 (AI) 股票的訊號。</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>earnings miss</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>293100070</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>fcb1015ed29a45f1b27aa8182eb9d53b</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>5e4c255072a524bad2b645d6</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>280826a9a8d021b3b0a3a85c</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+      <c r="AK26" s="2" t="inlineStr"/>
+      <c r="AL26" s="2" t="inlineStr"/>
+      <c r="AM26" s="2" t="inlineStr"/>
+      <c r="AN26" s="2" t="inlineStr"/>
+      <c r="AO26" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="3" t="inlineStr"/>
-      <c r="R26" s="3" t="inlineStr"/>
-      <c r="S26" s="3" t="inlineStr"/>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxObjRCOVFHWFRBVlhfMVVrbVl1cTB5MG1NZkZpV1V6ZlJoLUF5RnBuN0JBTFJDeVg3MC1vdU5JbGZ1UndMT3VvU2ozXzhKVGtvMFVodEFQSlZzOXFfYmFPV2o2bG8xMjI4Q0h2N1ZkS1Z4RVJ2a1dlQ3NNTUNhZHVlSVkxcnRZNWRNc1kxdVVadkRQLVZodUtNcDJn?oc=5</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t>Meta 的獲利未達標後，Cathie Wood 的方舟紛紛買進英偉達和台積電。以下是人工智慧 (AI) 股票的訊號。</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t>earnings miss</t>
-        </is>
-      </c>
-      <c r="AA26" s="3" t="inlineStr">
-        <is>
-          <t>293100070</t>
-        </is>
-      </c>
-      <c r="AB26" s="3" t="inlineStr"/>
-      <c r="AC26" s="3" t="inlineStr">
-        <is>
-          <t>5e4c255072a524bad2b645d6</t>
-        </is>
-      </c>
-      <c r="AD26" s="3" t="inlineStr">
-        <is>
-          <t>280826a9a8d021b3b0a3a85c</t>
-        </is>
-      </c>
-      <c r="AE26" s="3" t="inlineStr"/>
-      <c r="AF26" s="3" t="inlineStr"/>
-      <c r="AG26" s="3" t="inlineStr"/>
-      <c r="AH26" s="3" t="inlineStr"/>
-      <c r="AI26" s="3" t="inlineStr"/>
-      <c r="AJ26" s="3" t="inlineStr"/>
-      <c r="AK26" s="3" t="inlineStr"/>
-      <c r="AL26" s="3" t="inlineStr"/>
-      <c r="AM26" s="3" t="inlineStr"/>
-      <c r="AN26" s="3" t="inlineStr"/>
-      <c r="AO26" s="3" t="inlineStr"/>
-      <c r="AP26" s="3" t="inlineStr"/>
-      <c r="AQ26" s="3" t="inlineStr"/>
-      <c r="AR26" s="3" t="inlineStr"/>
-      <c r="AS26" s="3" t="inlineStr"/>
-      <c r="AT26" s="3" t="inlineStr"/>
-      <c r="AU26" s="3" t="inlineStr"/>
-      <c r="AV26" s="3" t="inlineStr"/>
-      <c r="AW26" s="3" t="inlineStr">
+      <c r="AP26" s="2" t="inlineStr"/>
+      <c r="AQ26" s="2" t="inlineStr"/>
+      <c r="AR26" s="2" t="inlineStr"/>
+      <c r="AS26" s="2" t="inlineStr"/>
+      <c r="AT26" s="2" t="inlineStr"/>
+      <c r="AU26" s="2" t="inlineStr"/>
+      <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX26" s="3" t="inlineStr"/>
-      <c r="AY26" s="3" t="inlineStr"/>
-      <c r="AZ26" s="3" t="inlineStr"/>
-      <c r="BA26" s="3" t="inlineStr"/>
-      <c r="BB26" s="3" t="inlineStr">
+      <c r="AX26" s="2" t="inlineStr"/>
+      <c r="AY26" s="2" t="inlineStr"/>
+      <c r="AZ26" s="2" t="inlineStr"/>
+      <c r="BA26" s="2" t="inlineStr"/>
+      <c r="BB26" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="BC26" s="3" t="inlineStr">
+      <c r="BC26" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD26" s="3" t="inlineStr"/>
-      <c r="BE26" s="3" t="inlineStr">
+      <c r="BD26" s="2" t="inlineStr"/>
+      <c r="BE26" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF26" s="3" t="inlineStr">
+      <c r="BF26" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG26" s="3" t="inlineStr">
+      <c r="BG26" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH26" s="3" t="inlineStr"/>
-      <c r="BI26" s="3" t="inlineStr"/>
-      <c r="BJ26" s="3" t="inlineStr"/>
-      <c r="BK26" s="3" t="inlineStr"/>
-      <c r="BL26" s="3" t="inlineStr"/>
+      <c r="BH26" s="2" t="inlineStr"/>
+      <c r="BI26" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL26"/>
@@ -5476,7 +5716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL14"/>
+  <dimension ref="A1:BL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5916,13 +6156,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -5979,7 +6223,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>1443ee69f56e4ef0bd40975d9097ea5a</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>05ea2f18bd4f2851b43711a7</t>
@@ -6000,7 +6248,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -6046,190 +6298,218 @@
       <c r="BH2" s="3" t="inlineStr"/>
       <c r="BI2" s="3" t="inlineStr"/>
       <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>EchoStar</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09T22:07:32+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Deal wins playoff over Bair for Echo Hills Club Championship title</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09T22:06:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Intuit Inc. (NASDAQ: INTU) Investors: September 8, 2026, Deadline in Securities Fraud Class Action Lawsuit - Contact Kessler Topaz Meltzer &amp; Check, LLP</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>'-0.107</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxQZmpfblFCWF9EbDhLd1c4VXJlMzJ0UEpoYmR3eDlBZTFhbmZSUW5RcFhjRnNEcGswUEFUTGwxWV9MUEhPTDlQa2JZbFJKTFd3WjNQTmQtWFRnaUtNWWhQVHlldl9CMTRtN3ZObExVdjN1Z185eFdMa0pCSnRXRGxfdlNNV2s4UHZQdzh3WDBoVE44X1g5cVMtck5pMjF4c2gxY09ZOVFIQWl4Vk1hYnI5eDNsT1RnRzN0OTF3MVZ4ZG5XSFFDdDdUbzdlY3BqWUhKQ205c1lraUFkWnFFRllqOVhCWlFELUIzeWcwZDJJZU00NDFVTm9ZanFWZURfaTRSWUt4TWoxWDRmdi05cUxwc1FNaWxrSmljZWMya1NBdU0wbnY1aVE?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>Intuit Inc.（納斯達克股票代碼：INTU）投資者：2026 年 9 月 8 日，證券詐欺集體訴訟截止日期 - 聯絡 Kessler Topaz Meltzer &amp; Check, LLP</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>6423132cd56444d393b2b5386bc53c6c</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>c10fdaeb2e765f7f30fab8c5</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>580eab8a5130e6f0639929ac</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr"/>
+      <c r="AF3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
+      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AM3" s="4" t="inlineStr"/>
+      <c r="AN3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>0.638</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeDRad0wtclZ2NmJWRnpFLUZCS240ZEFUM2dIYmMwQWwtcV92a25vcFVaMmlCRGVVREhOZkNZQnRfa1J3eWlfZWRSWGNEcnJsT1dOd3NvVHRkbmlBaTRaV0Y1N0R4NFNoakRpc1BUSld5SlBBR0hHU0FvUW9YbHp2WUZzcklfNWZSN1lQbEtCbGNfV05IbW5MWnFFR2Y?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Miami Valley Today</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>迪爾在延長賽中擊敗貝爾，奪得迴聲山俱樂部錦標賽冠軍</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>1f19875bdcd0ab2b6dd34fe2</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>c2bdafc09c6b8f06461d7001</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr"/>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>ECHO</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="3" t="inlineStr">
-        <is>
-          <t>ECHO</t>
-        </is>
-      </c>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="AP3" s="4" t="inlineStr"/>
+      <c r="AQ3" s="4" t="inlineStr"/>
+      <c r="AR3" s="4" t="inlineStr"/>
+      <c r="AS3" s="4" t="inlineStr"/>
+      <c r="AT3" s="4" t="inlineStr"/>
+      <c r="AU3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX3" s="4" t="inlineStr"/>
+      <c r="AY3" s="4" t="inlineStr"/>
+      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="BC3" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD3" s="4" t="inlineStr"/>
+      <c r="BE3" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr">
+      <c r="BF3" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="3" t="inlineStr"/>
-      <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
-      <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BG3" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -6254,12 +6534,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T22:06:00+08:00</t>
+          <t>2026-08-09T19:00:00+08:00</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Intuit Inc. (NASDAQ: INTU) Investors: September 8, 2026, Deadline in Securities Fraud Class Action Lawsuit - Contact Kessler Topaz Meltzer &amp; Check, LLP</t>
+          <t>2026-08-09 | INTU SHAREHOLDER ALERT: Bronstein, Gewirtz and Grossman, LLC Announces that Intuit Inc. Shareholders Have Opportunity to Lead Class Action Lawsuit! | NDAQ:INTU | Press Release</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -6300,7 +6580,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>'-0.107</t>
+          <t>'-0.486</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr"/>
@@ -6314,17 +6594,17 @@
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxQZmpfblFCWF9EbDhLd1c4VXJlMzJ0UEpoYmR3eDlBZTFhbmZSUW5RcFhjRnNEcGswUEFUTGwxWV9MUEhPTDlQa2JZbFJKTFd3WjNQTmQtWFRnaUtNWWhQVHlldl9CMTRtN3ZObExVdjN1Z185eFdMa0pCSnRXRGxfdlNNV2s4UHZQdzh3WDBoVE44X1g5cVMtck5pMjF4c2gxY09ZOVFIQWl4Vk1hYnI5eDNsT1RnRzN0OTF3MVZ4ZG5XSFFDdDdUbzdlY3BqWUhKQ205c1lraUFkWnFFRllqOVhCWlFELUIzeWcwZDJJZU00NDFVTm9ZanFWZURfaTRSWUt4TWoxWDRmdi05cUxwc1FNaWxrSmljZWMya1NBdU0wbnY1aVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNUUpVcDVLTzRKSENqLXRnMDIyTVV5N1R2U1pvVXVpTUtKckRvOV8zZ09CY0YwcGJmbnZEbWlHZjhodFpPeUlSOWg5c0o3NUVDamUyZXhjSE5jYnEzV3BkWGdOTl9hX01EcUU4OVFISldGcncyRDFaSS1oLVNybk00UzVUMHBkOWZiUG0zUkRlcV9OOTlwbXVNaV84SGx0OHVzQl9HTHFrYVZXU1ZLN0o2WG1hS3B3XzUxYzlEaUNxVmt0UVFWSWlxY3JzSEtjZw?oc=5</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>stockhouse.com</t>
         </is>
       </c>
       <c r="W4" s="4" t="inlineStr">
         <is>
-          <t>Intuit Inc.（納斯達克股票代碼：INTU）投資者：2026 年 9 月 8 日，證券詐欺集體訴訟截止日期 - 聯絡 Kessler Topaz Meltzer &amp; Check, LLP</t>
+          <t>2026-08-09 | INTU 股東提醒：Bronstein、Gewirtz 和 Grossman, LLC 宣布 Intuit Inc. 股東有機會提起集體訴訟！ |納斯達克：INTU |新聞稿</t>
         </is>
       </c>
       <c r="X4" s="4" t="inlineStr">
@@ -6349,17 +6629,17 @@
       </c>
       <c r="AB4" s="4" t="inlineStr">
         <is>
-          <t>6423132cd56444d393b2b5386bc53c6c</t>
+          <t>612c7ecfa6bb4f84b3e2ce138df2ee65</t>
         </is>
       </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
-          <t>c10fdaeb2e765f7f30fab8c5</t>
+          <t>c631ff786a3d33efd44687e1</t>
         </is>
       </c>
       <c r="AD4" s="4" t="inlineStr">
         <is>
-          <t>580eab8a5130e6f0639929ac</t>
+          <t>ba82d159fb91412492dcf49e</t>
         </is>
       </c>
       <c r="AE4" s="4" t="inlineStr"/>
@@ -6446,22 +6726,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>FedEx Corporation Common Stock</t>
+          <t>General Motors</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09T20:40:42+08:00</t>
+          <t>2026-08-09T18:01:00+08:00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Alex Fitzpatrick is ready to go deep in his first FedEx Cup playoffs run</t>
+          <t>Fate of laid-off CAMI workers part of upcoming GM-Unifor negotiations</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -6482,13 +6762,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -6498,7 +6782,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>'-0.923</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
@@ -6512,17 +6796,17 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQSU9ybDZaZmJVZlhrbW1JSkJGcGlnc2xGTTFFZjAtZHNGbW4xSVhNSXRxMVlyVW9PbFpuTHgta1o0QXRQMnk5dUdLcGoyYjIxaXY0a1lPZmNaOWp0UERqNEZiWHhOUDlXSF9XblFDTzlKRGZ2VjEycFJheEpTMEtDRC1aa1FFd21aTXl2TkFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxORzFoeTI3MGpFYXJvTDRzam1ObXZVY1dTOGp2NW1WaE5leFRsdFhLMDNyOHhjSmxOVWJuZ2NCTDNONjM1WU1TSlpVaE1TZVczVmFSYUtuOVh2X01lWVlkbEdocUlaaHJfa0VlRzBiUFdFanBsbEh5WkJJeWNwejdjQVVVbzRMWlREeXdNdF9MYmgyaDdTQ0ZwUjQ2SUI3a0NmNlQtOUJiazhYZkhWNU5QdHlVWTU0dw?oc=5</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>GOLF.com</t>
+          <t>Detroit Free Press</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>亞歷克斯·菲茨帕特里克（Alex Fitzpatrick）已準備好在他的第一次聯邦快遞杯季後賽中走得更遠</t>
+          <t>下崗 CAMI 工人的命運是即將舉行的通用汽車與 Unifor 談判的一部分</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
@@ -6537,7 +6821,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>layoff；layoffs</t>
+          <t>laid-off</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -6545,15 +6829,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>02a79b9a3a3a4b6d8d167bebc1b9476d</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>7bfea9cf408b7de8f418e2ca</t>
+          <t>29a92f5e77588e2b98a8c624</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>ed77bc1b0a1dcb3c2e4c6b4b</t>
+          <t>ed3a476a6b2cbf3ed232c23f</t>
         </is>
       </c>
       <c r="AE5" s="3" t="inlineStr"/>
@@ -6566,7 +6854,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -6574,18 +6866,14 @@
       <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="inlineStr"/>
       <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW5" s="3" t="inlineStr"/>
       <c r="AX5" s="3" t="inlineStr"/>
       <c r="AY5" s="3" t="inlineStr"/>
       <c r="AZ5" s="3" t="inlineStr"/>
       <c r="BA5" s="3" t="inlineStr"/>
       <c r="BB5" s="3" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="BC5" s="3" t="inlineStr">
@@ -6596,1673 +6884,225 @@
       <c r="BD5" s="3" t="inlineStr"/>
       <c r="BE5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF5" s="3" t="inlineStr"/>
       <c r="BG5" s="3" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
       <c r="BI5" s="3" t="inlineStr"/>
       <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr"/>
-      <c r="BL5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09T19:09:00+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>I went from wedding DJ to Meta engineer, then was laid off after 13 years. My last years there brought constant change.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>TSCO</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Tractor Supply</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:10:06+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Regional: Tractor Supply Company Subsidiary Agrees To $5.1 Million Consumer Protection Settlement</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>0.863</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPTjJnMzBOdnpWNDRxazl0ako0czBYd0tJNFNRcFhGZ1kzdVU1VXVaaFBDZ1VMRGZJa3VWTVNkRnZwVVBCT1hnSVNOdkhYcHVVRTZCeUxuX2k0aVZHTkVVX2xGelJHRVJjUGV6aXlLS29CMjR1cWY0QVJHbU9oZU1PaFJJU1BURUhqZXl3bm8xUWlwZEdOS0dEY3pxUnJyc0RC?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>SFGATE</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>地區：拖拉機供應公司子公司同意 510 萬美元消費者保護和解</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>1a7594200ecd4fe0a13ffd8896062149</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>5bd8af0daacf9ce043d01849</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>95e074d78dd7e4a6b1c56e9c</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>'-0.302</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOeGdTcDRTQWVRQ1NqcWZ2ZkpVemtWOE0yaGlpOVNjVXk5d3ZxSjh6elJ6WWNyVTROWlBaUkVfTlZRX1RJeUhTdW50NGtwaEZ1VncxSi13cVRBTm80NlVudkRoR2RwbUZkNXhaLWhtU29vT3I2bmNOV2ItQ1BvVHNtcDVUYmZtZHpzd1h6eFNtcXl2a3Rkbm9VcGUyR1ZsR04tWUFpeQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>businessinsider.com</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
-          <t>我從婚禮 DJ 到 Meta 工程師，13 年後被解僱。我在那裡的最後幾年帶來了不斷的變化。</t>
-        </is>
-      </c>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>laid off</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr">
-        <is>
-          <t>10900000</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>431c52efe5ad951117d3c27a</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>8e03bc4197a55663030cac41</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr"/>
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
+        <is>
+          <t>TSCO</t>
+        </is>
+      </c>
+      <c r="BC6" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG6" s="3" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
-      <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>INTU</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Intuit Inc.</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-09T19:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-09 | INTU SHAREHOLDER ALERT: Bronstein, Gewirtz and Grossman, LLC Announces that Intuit Inc. Shareholders Have Opportunity to Lead Class Action Lawsuit! | NDAQ:INTU | Press Release</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>'-0.486</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNUUpVcDVLTzRKSENqLXRnMDIyTVV5N1R2U1pvVXVpTUtKckRvOV8zZ09CY0YwcGJmbnZEbWlHZjhodFpPeUlSOWg5c0o3NUVDamUyZXhjSE5jYnEzV3BkWGdOTl9hX01EcUU4OVFISldGcncyRDFaSS1oLVNybk00UzVUMHBkOWZiUG0zUkRlcV9OOTlwbXVNaV84SGx0OHVzQl9HTHFrYVZXU1ZLN0o2WG1hS3B3XzUxYzlEaUNxVmt0UVFWSWlxY3JzSEtjZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>stockhouse.com</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-09 | INTU 股東提醒：Bronstein、Gewirtz 和 Grossman, LLC 宣布 Intuit Inc. 股東有機會提起集體訴訟！ |納斯達克：INTU |新聞稿</t>
-        </is>
-      </c>
-      <c r="X7" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>612c7ecfa6bb4f84b3e2ce138df2ee65</t>
-        </is>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
-        <is>
-          <t>c631ff786a3d33efd44687e1</t>
-        </is>
-      </c>
-      <c r="AD7" s="4" t="inlineStr">
-        <is>
-          <t>ba82d159fb91412492dcf49e</t>
-        </is>
-      </c>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
-        <is>
-          <t>INTU</t>
-        </is>
-      </c>
-      <c r="BC7" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH7" s="4" t="inlineStr"/>
-      <c r="BI7" s="4" t="inlineStr"/>
-      <c r="BJ7" s="4" t="inlineStr"/>
-      <c r="BK7" s="4" t="inlineStr">
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr"/>
+      <c r="BG6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL7" s="4" t="inlineStr">
+      <c r="BL6" s="4" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Electronic Arts</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09T18:54:48+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Purchase of Electronic Arts by Saudi group generates warning of mass layoffs</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>'-0.955</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQVmZ3QzhqTThuZWtzLV9NV0ZyLWtManYxS1liZF9ncUZsM0VSSHprY0Qza1ByQkFsNkI2UVdqM2hoaUZjblN5NExURENFOEZuTUw2MUg2OTZXd1VEVW9aS1lVbUNjajQwNkJfWHBQNHdBM21PR2hKdkNMNlJ6SDdvaTg2V3lVWVhJXzJtUTVYdm1XbXVmZFBYUk9oTzB2WFJxWHlRRG9UaHpyRGp0dFR0a0RqRFdOM3FVNWfSAb8BQVVfeXFMTmc4czN3QTE0TlJ4VXJXODYydmNHOUd3VFgxT0NsTWo1bG1MVk9Xd0VhYUlJX2hId0hzeXdXYXdMOFVpM2p0VW1JcE9OMnRvYllId2l5Umd2UzB0RUJWWUlEUmd4UkhWZEZmRUt1d2FuOUd5WGN1QnQ0bC13ZFJvOUt5c0dfSDRUUGdvaGpoNGlWRU5xbHBsQ1gxaHA5M3k4REtfLWtRWGd6dHJGd05mYzJsSHRLX1dFRlRwQm9sX1E?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>Mix Vale</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t>沙烏地阿拉伯集團收購美國藝電公司引發大規模裁員警告</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>ed6d1fe8449d2d1dfa7746f1</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>9802e53e707a47fde34f073b</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr"/>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF8" s="3" t="inlineStr"/>
-      <c r="BG8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr"/>
-      <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr"/>
-      <c r="BL8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Electronic Arts</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09T18:42:04+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Purchase of Electronic Arts by Arabs generates huge debt and risk of layoffs</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>'-0.957</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPWG5BWmZXUmM1eUFLNlgzbnFSby0tNndlYmRFN0c1ZW53Q3BkZ3lwbElQdGpILU1rV2hrY01qSDN5TlBhWWVWX1R4RnVyWUs0Y2NzOU9OcktleVBaYlc4Z3M3T3dqOEZSU292QmZ4ajVQM1lucG14bmtGU3FRakJ1ZFk1YnlDNXNZNUFGd2VhZUZkQTZpb1R1cUNGakFHR2llYmExQ0pBQmxwejFLY19aS2pzUllKWUc5M0ZNVGVPMNIBvwFBVV95cUxPWG5BWmZXUmM1eUFLNlgzbnFSby0tNndlYmRFN0c1ZW53Q3BkZ3lwbElQdGpILU1rV2hrY01qSDN5TlBhWWVWX1R4RnVyWUs0Y2NzOU9OcktleVBaYlc4Z3M3T3dqOEZSU292QmZ4ajVQM1lucG14bmtGU3FRakJ1ZFk1YnlDNXNZNUFGd2VhZUZkQTZpb1R1cUNGakFHR2llYmExQ0pBQmxwejFLY19aS2pzUllKWUc5M0ZNVGVPMA?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>Mix Vale</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t>阿拉伯人購買電子藝界產生巨額債務和裁員風險</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>d0244f171d6d53b850bba8b6</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>e34c38cf5b7e2c7d5bad963e</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr"/>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="BC9" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF9" s="3" t="inlineStr"/>
-      <c r="BG9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
-      <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr"/>
-      <c r="BL9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>General Motors</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09T18:01:00+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Fate of laid-off CAMI workers part of upcoming GM-Unifor negotiations</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>'-0.923</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxORzFoeTI3MGpFYXJvTDRzam1ObXZVY1dTOGp2NW1WaE5leFRsdFhLMDNyOHhjSmxOVWJuZ2NCTDNONjM1WU1TSlpVaE1TZVczVmFSYUtuOVh2X01lWVlkbEdocUlaaHJfa0VlRzBiUFdFanBsbEh5WkJJeWNwejdjQVVVbzRMWlREeXdNdF9MYmgyaDdTQ0ZwUjQ2SUI3a0NmNlQtOUJiazhYZkhWNU5QdHlVWTU0dw?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>Detroit Free Press</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t>下崗 CAMI 工人的命運是即將舉行的通用汽車與 Unifor 談判的一部分</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>laid-off</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
-        <is>
-          <t>29a92f5e77588e2b98a8c624</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>ed3a476a6b2cbf3ed232c23f</t>
-        </is>
-      </c>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr"/>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="BC10" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF10" s="3" t="inlineStr"/>
-      <c r="BG10" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr"/>
-      <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr"/>
-      <c r="BL10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>TSCO</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Tractor Supply</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-09T17:10:06+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Regional: Tractor Supply Company Subsidiary Agrees To $5.1 Million Consumer Protection Settlement</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>0.863</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPTjJnMzBOdnpWNDRxazl0ako0czBYd0tJNFNRcFhGZ1kzdVU1VXVaaFBDZ1VMRGZJa3VWTVNkRnZwVVBCT1hnSVNOdkhYcHVVRTZCeUxuX2k0aVZHTkVVX2xGelJHRVJjUGV6aXlLS29CMjR1cWY0QVJHbU9oZU1PaFJJU1BURUhqZXl3bm8xUWlwZEdOS0dEY3pxUnJyc0RC?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>SFGATE</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr">
-        <is>
-          <t>地區：拖拉機供應公司子公司同意 510 萬美元消費者保護和解</t>
-        </is>
-      </c>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="4" t="inlineStr">
-        <is>
-          <t>1a7594200ecd4fe0a13ffd8896062149</t>
-        </is>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>5bd8af0daacf9ce043d01849</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>95e074d78dd7e4a6b1c56e9c</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="4" t="inlineStr"/>
-      <c r="AS11" s="4" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr"/>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="4" t="inlineStr"/>
-      <c r="AZ11" s="4" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr">
-        <is>
-          <t>TSCO</t>
-        </is>
-      </c>
-      <c r="BC11" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD11" s="4" t="inlineStr"/>
-      <c r="BE11" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF11" s="4" t="inlineStr"/>
-      <c r="BG11" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH11" s="4" t="inlineStr"/>
-      <c r="BI11" s="4" t="inlineStr"/>
-      <c r="BJ11" s="4" t="inlineStr"/>
-      <c r="BK11" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09T17:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft releases Windows XP patch for WannaCrypt ransomware</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>資安攻擊</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>'-0.128</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9NZ2RVR0VfTUUyS2lzbmVEaWpmb3BsUWRyWjBkRko3WnJvVllhZlR1NVdwUG9VVmo2bnJZMDdVQ3RMTUNsckp0YWg1bnFqZ2dRMFNkbzd6akU2SDYtQkJyVE9ZRThBdjhO?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>Mashable</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t>微軟發布針對 WannaCrypt 勒索軟體的 Windows XP 補丁</t>
-        </is>
-      </c>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>CYBER_ATTACK</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>ransomware</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr">
-        <is>
-          <t>95500380</t>
-        </is>
-      </c>
-      <c r="AB12" s="3" t="inlineStr"/>
-      <c r="AC12" s="3" t="inlineStr">
-        <is>
-          <t>f1c7e7eb799e067053d54d0c</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>92d1743eeade3cb6fad4a889</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="BC12" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH12" s="3" t="inlineStr"/>
-      <c r="BI12" s="3" t="inlineStr"/>
-      <c r="BJ12" s="3" t="inlineStr"/>
-      <c r="BK12" s="3" t="inlineStr"/>
-      <c r="BL12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09T16:05:00+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Cathie Wood's Ark Piled Into Nvidia and Taiwan Semiconductor After Meta's Earnings Miss. Here's What It Signals for Artificial Intelligence (AI) Stocks.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPb0d5bGJQOS1EY1FQUjMzcDRnZEVod1NwS2dJRUhraElXbTY3aXQ5Zk5uOXRJWDd2NUxIaEprejl5a2VjWTF0VS1BNlZQWnRUTnF6OG9mQl95YjgwMUtfNmRiNlpiWXRmOHctVXZ6NEI3WERiNkdwWVFJZjRRYjRVdk5aeWlTeElvR3dVeWtVX2l0ckRmVG9kNg?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t>The Motley Fool</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr">
-        <is>
-          <t>Meta 的獲利未達標後，Cathie Wood 的方舟紛紛買進英偉達和台積電。以下是人工智慧 (AI) 股票的訊號。</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t>earnings miss</t>
-        </is>
-      </c>
-      <c r="AA13" s="3" t="inlineStr">
-        <is>
-          <t>10900000</t>
-        </is>
-      </c>
-      <c r="AB13" s="3" t="inlineStr"/>
-      <c r="AC13" s="3" t="inlineStr">
-        <is>
-          <t>40397b1a8e3afd65041296c3</t>
-        </is>
-      </c>
-      <c r="AD13" s="3" t="inlineStr">
-        <is>
-          <t>705eabf69f239b628c12d34f</t>
-        </is>
-      </c>
-      <c r="AE13" s="3" t="inlineStr"/>
-      <c r="AF13" s="3" t="inlineStr"/>
-      <c r="AG13" s="3" t="inlineStr"/>
-      <c r="AH13" s="3" t="inlineStr"/>
-      <c r="AI13" s="3" t="inlineStr"/>
-      <c r="AJ13" s="3" t="inlineStr"/>
-      <c r="AK13" s="3" t="inlineStr"/>
-      <c r="AL13" s="3" t="inlineStr"/>
-      <c r="AM13" s="3" t="inlineStr"/>
-      <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
-      <c r="AP13" s="3" t="inlineStr"/>
-      <c r="AQ13" s="3" t="inlineStr"/>
-      <c r="AR13" s="3" t="inlineStr"/>
-      <c r="AS13" s="3" t="inlineStr"/>
-      <c r="AT13" s="3" t="inlineStr"/>
-      <c r="AU13" s="3" t="inlineStr"/>
-      <c r="AV13" s="3" t="inlineStr"/>
-      <c r="AW13" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX13" s="3" t="inlineStr"/>
-      <c r="AY13" s="3" t="inlineStr"/>
-      <c r="AZ13" s="3" t="inlineStr"/>
-      <c r="BA13" s="3" t="inlineStr"/>
-      <c r="BB13" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="BC13" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD13" s="3" t="inlineStr"/>
-      <c r="BE13" s="3" t="inlineStr">
-        <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG13" s="3" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH13" s="3" t="inlineStr"/>
-      <c r="BI13" s="3" t="inlineStr"/>
-      <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr"/>
-      <c r="BL13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09T15:25:00+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Cathie Wood's Ark Piled Into Nvidia and Taiwan Semiconductor After Meta's Earnings Miss. Here's What It Signals for Artificial Intelligence (AI) Stocks.</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxObjRCOVFHWFRBVlhfMVVrbVl1cTB5MG1NZkZpV1V6ZlJoLUF5RnBuN0JBTFJDeVg3MC1vdU5JbGZ1UndMT3VvU2ozXzhKVGtvMFVodEFQSlZzOXFfYmFPV2o2bG8xMjI4Q0h2N1ZkS1Z4RVJ2a1dlQ3NNTUNhZHVlSVkxcnRZNWRNc1kxdVVadkRQLVZodUtNcDJn?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t>Meta 的獲利未達標後，Cathie Wood 的方舟紛紛買進英偉達和台積電。以下是人工智慧 (AI) 股票的訊號。</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>earnings miss</t>
-        </is>
-      </c>
-      <c r="AA14" s="3" t="inlineStr">
-        <is>
-          <t>293100070</t>
-        </is>
-      </c>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="inlineStr">
-        <is>
-          <t>5e4c255072a524bad2b645d6</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>280826a9a8d021b3b0a3a85c</t>
-        </is>
-      </c>
-      <c r="AE14" s="3" t="inlineStr"/>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="BC14" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD14" s="3" t="inlineStr"/>
-      <c r="BE14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG14" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH14" s="3" t="inlineStr"/>
-      <c r="BI14" s="3" t="inlineStr"/>
-      <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr"/>
-      <c r="BL14" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL14"/>
+  <autoFilter ref="A1:BL6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8273,7 +7113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL3"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8664,372 +7504,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>EchoStar</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09T22:07:32+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Deal wins playoff over Bair for Echo Hills Club Championship title</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>0.638</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeDRad0wtclZ2NmJWRnpFLUZCS240ZEFUM2dIYmMwQWwtcV92a25vcFVaMmlCRGVVREhOZkNZQnRfa1J3eWlfZWRSWGNEcnJsT1dOd3NvVHRkbmlBaTRaV0Y1N0R4NFNoakRpc1BUSld5SlBBR0hHU0FvUW9YbHp2WUZzcklfNWZSN1lQbEtCbGNfV05IbW5MWnFFR2Y?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>Miami Valley Today</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
-        <is>
-          <t>迪爾在延長賽中擊敗貝爾，奪得迴聲山俱樂部錦標賽冠軍</t>
-        </is>
-      </c>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="inlineStr"/>
-      <c r="AC2" s="3" t="inlineStr">
-        <is>
-          <t>1f19875bdcd0ab2b6dd34fe2</t>
-        </is>
-      </c>
-      <c r="AD2" s="3" t="inlineStr">
-        <is>
-          <t>c2bdafc09c6b8f06461d7001</t>
-        </is>
-      </c>
-      <c r="AE2" s="3" t="inlineStr"/>
-      <c r="AF2" s="3" t="inlineStr"/>
-      <c r="AG2" s="3" t="inlineStr"/>
-      <c r="AH2" s="3" t="inlineStr"/>
-      <c r="AI2" s="3" t="inlineStr"/>
-      <c r="AJ2" s="3" t="inlineStr"/>
-      <c r="AK2" s="3" t="inlineStr"/>
-      <c r="AL2" s="3" t="inlineStr"/>
-      <c r="AM2" s="3" t="inlineStr"/>
-      <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="3" t="inlineStr"/>
-      <c r="AQ2" s="3" t="inlineStr"/>
-      <c r="AR2" s="3" t="inlineStr"/>
-      <c r="AS2" s="3" t="inlineStr"/>
-      <c r="AT2" s="3" t="inlineStr"/>
-      <c r="AU2" s="3" t="inlineStr"/>
-      <c r="AV2" s="3" t="inlineStr"/>
-      <c r="AW2" s="3" t="inlineStr"/>
-      <c r="AX2" s="3" t="inlineStr"/>
-      <c r="AY2" s="3" t="inlineStr"/>
-      <c r="AZ2" s="3" t="inlineStr"/>
-      <c r="BA2" s="3" t="inlineStr"/>
-      <c r="BB2" s="3" t="inlineStr">
-        <is>
-          <t>ECHO</t>
-        </is>
-      </c>
-      <c r="BC2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="3" t="inlineStr">
-        <is>
-          <t>ECHO</t>
-        </is>
-      </c>
-      <c r="BE2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="3" t="inlineStr"/>
-      <c r="BH2" s="3" t="inlineStr"/>
-      <c r="BI2" s="3" t="inlineStr"/>
-      <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Ulta Beauty</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-09T16:59:06+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>I Can't Stop Spring Shopping (a Vlog): Old Navy Finds, Ulta, Costco For Two, Cooking, April Nuuly San Jose Earthquakes (zFaru3F51W)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>0.018</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBacDV3RjdGNU1JMEwyUGQ3cFRaeXg0NS0zRTRSRk9aSU85ajc1MVpGQmdQR3hYRk1nbm8wRGZZa29pMXo0VXJXSldlTTExRG1OZ09sVS1WUjgxZTg?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Mshale</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>我無法停止春季購物（視頻博客）：Old Navy Finds、Ulta、Costco For Two、烹飪、四月努利聖何塞地震 (zFaru3F51W)</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>cd5d4e0cf1ff0e21b41ac4fc</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>4be4a2f9e0356691efd1ab1f</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr"/>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>ULTA</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="2" t="inlineStr">
-        <is>
-          <t>ULTA</t>
-        </is>
-      </c>
-      <c r="BE3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="2" t="inlineStr"/>
-      <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL3"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-08-09.xlsx
+++ b/news_daily/2026-08-09.xlsx
@@ -1094,28 +1094,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1159,7 +1163,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1172,7 +1176,11 @@
           <t>163090500</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>75a9ff13c95f4537be31c5ab66f564f6</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>75256f60d07a0498bb303939</t>
@@ -1193,7 +1201,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1237,10 +1249,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1276,28 +1300,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1341,7 +1369,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1354,7 +1382,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>61e2d9037b3a4e98804dd3f3b9ab1c15</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>5e8244d29e61705a52bf238a</t>
@@ -1375,7 +1407,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1419,10 +1455,22 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1858,28 +1906,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1923,7 +1975,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1936,7 +1988,11 @@
           <t>163090500</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>5375e7356fdf4fcf8337a388d048f728</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>6f73cb75ccb99b381a6d2554</t>
@@ -1957,7 +2013,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -2001,10 +2061,22 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2440,28 +2512,32 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2505,7 +2581,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -2518,7 +2594,11 @@
           <t>22304000</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>85dc281c17c449c088da86387d18018d</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>704029b7b035a4dbdb69496b</t>
@@ -2539,7 +2619,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -2575,10 +2659,22 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
-      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3026,28 +3122,32 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3091,7 +3191,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -3104,7 +3204,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>32d8df55554f4b01bf2b49e66eee5f35</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>7330704ccef760d2fce28e7b</t>
@@ -3125,7 +3229,11 @@
       <c r="AL13" s="2" t="inlineStr"/>
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="2" t="inlineStr"/>
       <c r="AQ13" s="2" t="inlineStr"/>
       <c r="AR13" s="2" t="inlineStr"/>
@@ -3169,10 +3277,22 @@
         </is>
       </c>
       <c r="BH13" s="2" t="inlineStr"/>
-      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ13" s="2" t="inlineStr"/>
-      <c r="BK13" s="2" t="inlineStr"/>
-      <c r="BL13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -4000,28 +4120,32 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4065,7 +4189,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -4078,7 +4202,11 @@
           <t>10900000</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>ccf6a5ead8fb497e976ef18d2a5abac6</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>4542488899e1004c63cee3a7</t>
@@ -4099,7 +4227,11 @@
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
@@ -4143,10 +4275,22 @@
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
-      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ18" s="2" t="inlineStr"/>
-      <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4182,28 +4326,32 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4247,7 +4395,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -4260,7 +4408,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>e021734752104e5bb996ad6ee8973d0d</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>d4626aa7356535e02f6516e6</t>
@@ -4281,7 +4433,11 @@
       <c r="AL19" s="2" t="inlineStr"/>
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="2" t="inlineStr"/>
       <c r="AQ19" s="2" t="inlineStr"/>
       <c r="AR19" s="2" t="inlineStr"/>
@@ -4325,10 +4481,22 @@
         </is>
       </c>
       <c r="BH19" s="2" t="inlineStr"/>
-      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ19" s="2" t="inlineStr"/>
-      <c r="BK19" s="2" t="inlineStr"/>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -4558,28 +4726,32 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4623,7 +4795,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -4636,7 +4808,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>983a3c4e83ec4b3ebcf80370b95cd38f</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>c98d16a394e2f05c3ba46660</t>
@@ -4657,7 +4833,11 @@
       <c r="AL21" s="2" t="inlineStr"/>
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr"/>
-      <c r="AO21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="2" t="inlineStr"/>
       <c r="AQ21" s="2" t="inlineStr"/>
       <c r="AR21" s="2" t="inlineStr"/>
@@ -4701,10 +4881,22 @@
         </is>
       </c>
       <c r="BH21" s="2" t="inlineStr"/>
-      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ21" s="2" t="inlineStr"/>
-      <c r="BK21" s="2" t="inlineStr"/>
-      <c r="BL21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5350,28 +5542,32 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5415,7 +5611,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -5428,7 +5624,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>b3c6fe19324c46f4a2708d8bbaa6fb35</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
           <t>ac3b1da263b404c8833fca5b</t>
@@ -5449,7 +5649,11 @@
       <c r="AL25" s="2" t="inlineStr"/>
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr"/>
-      <c r="AO25" s="2" t="inlineStr"/>
+      <c r="AO25" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP25" s="2" t="inlineStr"/>
       <c r="AQ25" s="2" t="inlineStr"/>
       <c r="AR25" s="2" t="inlineStr"/>
@@ -5493,10 +5697,22 @@
         </is>
       </c>
       <c r="BH25" s="2" t="inlineStr"/>
-      <c r="BI25" s="2" t="inlineStr"/>
+      <c r="BI25" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ25" s="2" t="inlineStr"/>
-      <c r="BK25" s="2" t="inlineStr"/>
-      <c r="BL25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
